--- a/data/excel/HotelManualBooking.xlsx
+++ b/data/excel/HotelManualBooking.xlsx
@@ -3,17 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48F3659-421D-43B1-A0CE-AB559721D599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D830CD-E1B0-4EF7-868E-97F3DBB75B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="BODC" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="7" r:id="rId4"/>
-    <sheet name="BOCA" sheetId="6" r:id="rId5"/>
-    <sheet name="Sheet4" sheetId="8" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="9" r:id="rId5"/>
+    <sheet name="BOCA" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet4" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="172">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -472,6 +473,75 @@
   </si>
   <si>
     <t>Delux Room with king size bed</t>
+  </si>
+  <si>
+    <t>Gaurav Shah,Sumit Shah</t>
+  </si>
+  <si>
+    <t>Gaurav Travel</t>
+  </si>
+  <si>
+    <t>5-Aug-2024,5-Feb-2024</t>
+  </si>
+  <si>
+    <t>Deluxe Room</t>
+  </si>
+  <si>
+    <t>Gaurav Dubey,Sumit Shah</t>
+  </si>
+  <si>
+    <t>Piyush Chauhan,Sunita Shah</t>
+  </si>
+  <si>
+    <t>Ankur Yadav,Satish Shah</t>
+  </si>
+  <si>
+    <t>Saurav Shah,Sumit Shah</t>
+  </si>
+  <si>
+    <t>Sachin Singh,Sunita Shah</t>
+  </si>
+  <si>
+    <t>5-Aug-2024,5-Feb-2023</t>
+  </si>
+  <si>
+    <t>Blue Origin</t>
+  </si>
+  <si>
+    <t>Oberoi International</t>
+  </si>
+  <si>
+    <t>16-Sep-2025</t>
+  </si>
+  <si>
+    <t>20-Sep-2025</t>
+  </si>
+  <si>
+    <t>Super Deluxe Room</t>
+  </si>
+  <si>
+    <t>Exclusive Room</t>
+  </si>
+  <si>
+    <t>1 Breakfast with lunch</t>
+  </si>
+  <si>
+    <t>1 Breakfast with dessert</t>
+  </si>
+  <si>
+    <t>10,10,30</t>
+  </si>
+  <si>
+    <t>20,10,30</t>
+  </si>
+  <si>
+    <t>Baggage Charges,Meal Charges,Markup</t>
+  </si>
+  <si>
+    <t>10,10,10</t>
+  </si>
+  <si>
+    <t>18-Sep-2025</t>
   </si>
 </sst>
 </file>
@@ -572,7 +642,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -592,6 +662,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2955,6 +3036,7 @@
   <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3069,19 +3151,19 @@
       <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="19" t="s">
         <v>139</v>
       </c>
       <c r="I2" s="9">
@@ -3094,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="M2" t="s">
         <v>81</v>
@@ -3112,7 +3194,7 @@
         <v>107</v>
       </c>
       <c r="R2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="S2" t="s">
         <v>16</v>
@@ -3133,10 +3215,10 @@
         <v>9999999105</v>
       </c>
       <c r="Y2" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="Z2" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="AA2">
         <v>1</v>
@@ -3178,7 +3260,7 @@
       <formula1>"HK,RQ"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2" xr:uid="{2F693E2F-7A76-4AB0-9978-694775DE9563}">
-      <formula1>"ABC Supplier,ATsupplier,BSP Supplier,gaurav travel"</formula1>
+      <formula1>"ABC Supplier,ATsupplier,BSP Supplier,Gaurav Travel"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{C7E15ADA-5B5D-4937-859D-FB8522A37347}">
       <formula1>"at,qlabs12345,merg123456"</formula1>
@@ -3195,12 +3277,475 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{3FDBDC7E-63BF-4BA4-BA4A-9D82256C860C}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{B33B46B8-1A22-4297-B0E7-AEBE7007A78D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B0C20E-2E29-4A82-90DB-D17050FDAAD7}">
+  <dimension ref="A1:AG4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="I2" s="20">
+        <v>1</v>
+      </c>
+      <c r="J2" s="20">
+        <v>0</v>
+      </c>
+      <c r="K2" s="20">
+        <v>0</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="U2" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="V2" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" s="3">
+        <v>9999999112</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD2" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="I3" s="20">
+        <v>1</v>
+      </c>
+      <c r="J3" s="20">
+        <v>1</v>
+      </c>
+      <c r="K3" s="20">
+        <v>0</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X3" s="3">
+        <v>9999999113</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD3" s="20">
+        <v>2</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="I4" s="20">
+        <v>1</v>
+      </c>
+      <c r="J4" s="20">
+        <v>1</v>
+      </c>
+      <c r="K4" s="20">
+        <v>1</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="O4" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="U4" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="V4" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" s="3">
+        <v>9999999114</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD4" s="20">
+        <v>3</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4" xr:uid="{B2FDDF0F-B045-40E5-AB59-30D251997CF9}">
+      <formula1>"HK,RQ"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD4" xr:uid="{CF0CC205-9013-4CFB-A7F1-2C233D0BF111}">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC4" xr:uid="{998501D8-547D-4EFF-ADAD-AE4CD7986855}">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG4" xr:uid="{42179C95-BFE2-438A-8932-12BFDD17FDA0}">
+      <formula1>"Adjustment,Bank Draft,Inter Booking Transfer,Net Banking,Credit Card,Bank Transfer,Debit Card,Cash,Cheque,Direct Deposit"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K4" xr:uid="{28069E76-2B69-4855-9FED-F10E9E1E0995}">
+      <formula1>"0,1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G4" xr:uid="{909A0944-4748-48B0-A3C3-18A5539D391F}">
+      <formula1>"EE6B4B@E7,Ankur@12345,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D4" xr:uid="{FEE6D9D6-4DC9-4D52-8D51-AEDDE936F58F}">
+      <formula1>"//xchangev12/backoffice/Home.aspx, //v12staging/backoffice/"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4" xr:uid="{71B665D9-5060-4759-AA2A-A8F5C5AA2BF3}">
+      <formula1>"Piyush_ql,ankur_ql"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4" xr:uid="{282F5031-53BB-4F5C-BCC2-07CD344FD0D3}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R4" xr:uid="{70CED0D0-797C-4DCC-AE7A-ED8C7078C2E4}">
+      <formula1>"ABC Supplier,ATsupplier,BSP Supplier,Gaurav Travel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3" xr:uid="{2C4B34A5-45D7-4FEA-BE6E-678C1F4B4BB5}">
+      <formula1>"ABC Supplier,ATsupplier,BSP Supplier,gaurav travel"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H4" r:id="rId1" xr:uid="{2E2B4E58-E6DF-459A-A8E9-A05B33BB5653}"/>
+    <hyperlink ref="G4" r:id="rId2" xr:uid="{EEB502E6-75F7-49CE-A0A4-562A95447CC2}"/>
+    <hyperlink ref="H2" r:id="rId3" xr:uid="{44262B74-E2F1-443A-852F-268281B7848A}"/>
+    <hyperlink ref="G2" r:id="rId4" xr:uid="{C1E19A93-3F2C-4CF0-AA83-F78A45C846AA}"/>
+    <hyperlink ref="H3" r:id="rId5" xr:uid="{1E8EAE70-5827-450B-9512-476764D55A4E}"/>
+    <hyperlink ref="G3" r:id="rId6" xr:uid="{072CB44A-E97A-4F1F-A659-F21BDD6E9D7E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1B4D273-3F24-48EC-BE03-C6C1573B7DF3}">
   <dimension ref="A1:AG6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3889,7 +4434,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C638BED8-1E4D-4050-9764-D4033615FE19}">
   <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/data/excel/HotelManualBooking.xlsx
+++ b/data/excel/HotelManualBooking.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D830CD-E1B0-4EF7-868E-97F3DBB75B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DD4E7C-A5E1-40CF-9300-E1F793AFC30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="200">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -427,18 +427,9 @@
     <t>17-Sep-2024</t>
   </si>
   <si>
-    <t>ankur_QL</t>
-  </si>
-  <si>
-    <t>Ankur@12345</t>
-  </si>
-  <si>
     <t>piyush.chauhan@quadlabs.com</t>
   </si>
   <si>
-    <t>Ankush009@quadlabs.com</t>
-  </si>
-  <si>
     <t>ankur_ql</t>
   </si>
   <si>
@@ -542,13 +533,106 @@
   </si>
   <si>
     <t>18-Sep-2025</t>
+  </si>
+  <si>
+    <t>k.gaurav</t>
+  </si>
+  <si>
+    <t>E0@DA44FE</t>
+  </si>
+  <si>
+    <t>Sachin Shah,Sumit Shah</t>
+  </si>
+  <si>
+    <t>Sanjay Shah,Sumit Shah</t>
+  </si>
+  <si>
+    <t>Sumit Shah,Sumit Shah</t>
+  </si>
+  <si>
+    <t>Sanjiv Shah,Sumit Shah</t>
+  </si>
+  <si>
+    <t>18-Sep-2024</t>
+  </si>
+  <si>
+    <t>19-Sep-2024</t>
+  </si>
+  <si>
+    <t>20-Sep-2024</t>
+  </si>
+  <si>
+    <t>21-Sep-2024</t>
+  </si>
+  <si>
+    <t>23-Sep-2024</t>
+  </si>
+  <si>
+    <t>2 Breakfast</t>
+  </si>
+  <si>
+    <t>Italean meal</t>
+  </si>
+  <si>
+    <t>Continental meal</t>
+  </si>
+  <si>
+    <t>Japanese food</t>
+  </si>
+  <si>
+    <t>1 Indian Breakfast</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Standard Room</t>
+  </si>
+  <si>
+    <t>King size Room</t>
+  </si>
+  <si>
+    <t>Queen Room</t>
+  </si>
+  <si>
+    <t>Grand Hyatt</t>
+  </si>
+  <si>
+    <t>Reddison Blue</t>
+  </si>
+  <si>
+    <t>Hotel Taaj</t>
+  </si>
+  <si>
+    <t>OYO Exclusive</t>
+  </si>
+  <si>
+    <t>19-Sep-2025</t>
+  </si>
+  <si>
+    <t>21-Sep-2025</t>
+  </si>
+  <si>
+    <t>23-Sep-2025</t>
+  </si>
+  <si>
+    <t>Verify manual booking for hotel with 1 adult, 1 Child with meal</t>
+  </si>
+  <si>
+    <t>Verify manual booking for hotel with 1 adult, 1 child with base fare only</t>
+  </si>
+  <si>
+    <t>Verify manual booking for hotel with adult, child, infant with other charges</t>
+  </si>
+  <si>
+    <t>Verify manual booking for hotel with adult and infant with payment received</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -575,12 +659,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF555555"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -642,7 +720,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -654,7 +732,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -665,12 +742,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
@@ -2489,19 +2560,19 @@
       <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H2" s="11" t="s">
+      <c r="F2" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I2" s="9">
@@ -2541,31 +2612,31 @@
         <v>110</v>
       </c>
       <c r="U2" s="7" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="V2" s="7" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="W2" t="s">
         <v>24</v>
       </c>
       <c r="X2">
-        <v>9999999101</v>
+        <v>9999900101</v>
       </c>
       <c r="Y2" t="s">
         <v>116</v>
       </c>
       <c r="Z2" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AC2" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="AD2" s="9">
         <v>3</v>
@@ -2590,26 +2661,26 @@
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H3" s="11" t="s">
+      <c r="F3" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I3" s="9">
         <v>1</v>
       </c>
       <c r="J3" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="9">
         <v>0</v>
@@ -2642,31 +2713,31 @@
         <v>110</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="W3" t="s">
         <v>24</v>
       </c>
       <c r="X3">
-        <v>9999999102</v>
+        <v>9999900102</v>
       </c>
       <c r="Y3" t="s">
         <v>116</v>
       </c>
       <c r="Z3" t="s">
-        <v>118</v>
+        <v>180</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="AC3" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="AD3" s="9">
         <v>2</v>
@@ -2691,29 +2762,29 @@
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H4" s="11" t="s">
+      <c r="F4" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
       </c>
       <c r="J4" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="9" t="s">
         <v>80</v>
@@ -2743,28 +2814,28 @@
         <v>110</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="V4" s="7" t="s">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="W4" t="s">
         <v>24</v>
       </c>
       <c r="X4">
-        <v>9999999103</v>
+        <v>9999900103</v>
       </c>
       <c r="Y4" t="s">
         <v>116</v>
       </c>
       <c r="Z4" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AC4" t="s">
         <v>31</v>
@@ -2792,29 +2863,29 @@
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H5" s="11" t="s">
+      <c r="F5" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I5" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>80</v>
@@ -2844,28 +2915,28 @@
         <v>110</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="W5" t="s">
         <v>24</v>
       </c>
       <c r="X5">
-        <v>9999999104</v>
+        <v>9999900104</v>
       </c>
       <c r="Y5" t="s">
         <v>116</v>
       </c>
       <c r="Z5" t="s">
-        <v>118</v>
+        <v>182</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="AC5" t="s">
         <v>31</v>
@@ -2893,29 +2964,29 @@
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H6" s="11" t="s">
+      <c r="F6" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I6" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>80</v>
@@ -2945,28 +3016,28 @@
         <v>110</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="W6" t="s">
         <v>24</v>
       </c>
       <c r="X6">
-        <v>9999999105</v>
+        <v>9999900105</v>
       </c>
       <c r="Y6" t="s">
         <v>116</v>
       </c>
       <c r="Z6" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AC6" t="s">
         <v>31</v>
@@ -2986,13 +3057,10 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations count="9">
+  <dataValidations count="11">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K6" xr:uid="{2BF9A17B-8264-4700-A928-A4DB336C1293}">
       <formula1>"0,1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6" xr:uid="{997C06AD-95DE-46E9-A103-AB8581E765AB}">
-      <formula1>"at,qlabs12345"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG6" xr:uid="{4688F7E0-FA8B-42FE-B338-8F1C12A449F6}">
       <formula1>"Adjustment,Bank Draft,Inter Booking Transfer,Net Banking,Credit Card,Bank Transfer,Debit Card,Cash,Cheque,Direct Deposit"</formula1>
     </dataValidation>
@@ -3008,24 +3076,33 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R6" xr:uid="{C4067F69-FA98-44CB-87CB-336EA4A31BDB}">
       <formula1>"ABC Supplier,ATsupplier,BSP Supplier,gaurav travel"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G6" xr:uid="{9D849E6D-0572-4BCD-A837-F48EDADCB178}">
-      <formula1>"Password@@12,Gaurav@130,Ankur@12345"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6" xr:uid="{B301C82A-6DF7-42E7-A060-56B86DF17D94}">
-      <formula1>"Piyush_QL,k.gaurav,ankur_QL"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H6" xr:uid="{F975841A-C704-4D37-BC08-B658BFF406A2}">
+      <formula1>"kumar.gaurav@quadlabs.com,ankit@quadlabs.com,akshay.kumar@quadlabs.com"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G6" xr:uid="{4293C305-91E2-4519-B520-4F1AE36BC2D1}">
+      <formula1>"E0@DA44FE,Ankur@721,Piyush@12345"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6" xr:uid="{8A77924A-8E85-4078-950E-AFB8E2FB34F8}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D6" xr:uid="{3C872C6F-F9BD-40C5-9CFB-5361FD5A98D4}">
+      <formula1>"//xchangev12/backoffice/Home.aspx, //v12staging/backoffice/"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6" xr:uid="{B0A09F30-0278-4039-9B77-EDFBFEFE3031}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="shubham.natkar@quadlabs.com" xr:uid="{679E64FA-F7A4-440C-A770-18F6FB8E54B5}"/>
-    <hyperlink ref="G2" r:id="rId2" display="Piyush@321" xr:uid="{4F77F8A7-EE9B-40B7-B3DA-5979EEE3DE82}"/>
-    <hyperlink ref="F3" r:id="rId3" display="shubham.natkar@quadlabs.com" xr:uid="{4CF80D20-F189-4A66-8563-0EB18EDAC338}"/>
-    <hyperlink ref="G3" r:id="rId4" display="Piyush@321" xr:uid="{B86AB1E8-473B-4644-AAFB-B7E4BEFD16FD}"/>
-    <hyperlink ref="F4" r:id="rId5" display="shubham.natkar@quadlabs.com" xr:uid="{0A4AEE39-4DCD-4016-A91B-DFBC4F8DD768}"/>
-    <hyperlink ref="G4" r:id="rId6" display="Piyush@321" xr:uid="{5650DA51-EE5C-4079-BA99-C68A0DAD78B8}"/>
-    <hyperlink ref="F5" r:id="rId7" display="shubham.natkar@quadlabs.com" xr:uid="{FCD789AA-C3DC-4182-8219-C24B1E217E11}"/>
-    <hyperlink ref="G5" r:id="rId8" display="Piyush@321" xr:uid="{253CD65C-753E-4EF1-A5E9-9653E811E6C1}"/>
-    <hyperlink ref="F6" r:id="rId9" display="shubham.natkar@quadlabs.com" xr:uid="{DE904B68-71C6-448B-B113-15BB5E7AB969}"/>
-    <hyperlink ref="G6" r:id="rId10" display="Piyush@321" xr:uid="{9A34F604-6E9E-4C82-91D4-CE8462384A2F}"/>
+    <hyperlink ref="H2" r:id="rId1" display="ankit@quadlabs.com" xr:uid="{4FAFF3F4-AE7D-4759-94CD-66A7BA7DC34D}"/>
+    <hyperlink ref="G2" r:id="rId2" display="EE6B4B@E7" xr:uid="{19472581-76E4-46B0-9FA5-35BE2483F0BB}"/>
+    <hyperlink ref="H3" r:id="rId3" display="ankit@quadlabs.com" xr:uid="{383934BE-4E9F-420A-A583-DE801777226A}"/>
+    <hyperlink ref="G3" r:id="rId4" display="EE6B4B@E7" xr:uid="{DE194A8E-8DA0-49CC-A4C6-6B7D3446635E}"/>
+    <hyperlink ref="H4" r:id="rId5" display="ankit@quadlabs.com" xr:uid="{02102B68-C867-47E2-A710-091519C4E947}"/>
+    <hyperlink ref="G4" r:id="rId6" display="EE6B4B@E7" xr:uid="{FE93245A-6E5B-49AE-A8E1-511402EC71F7}"/>
+    <hyperlink ref="H5" r:id="rId7" display="ankit@quadlabs.com" xr:uid="{A6191047-2316-46A1-B396-03A3FE3F95EE}"/>
+    <hyperlink ref="G5" r:id="rId8" display="EE6B4B@E7" xr:uid="{4B00D0E0-1B66-4A83-B85E-FE39F0473256}"/>
+    <hyperlink ref="H6" r:id="rId9" display="ankit@quadlabs.com" xr:uid="{E2100583-3F44-4475-957A-5141F49C6660}"/>
+    <hyperlink ref="G6" r:id="rId10" display="EE6B4B@E7" xr:uid="{52093F40-2F87-4D2A-A967-28BC94B5D38B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3033,10 +3110,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED204D34-4B38-4CE6-B3A2-9F55432253BD}">
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AG6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3141,7 +3219,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -3151,20 +3229,20 @@
       <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>139</v>
+      <c r="F2" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -3176,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="M2" t="s">
         <v>81</v>
@@ -3194,7 +3272,7 @@
         <v>107</v>
       </c>
       <c r="R2" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="S2" t="s">
         <v>16</v>
@@ -3203,34 +3281,34 @@
         <v>110</v>
       </c>
       <c r="U2" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="V2" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="W2" t="s">
         <v>24</v>
       </c>
       <c r="X2">
-        <v>9999999105</v>
+        <v>9009910201</v>
       </c>
       <c r="Y2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z2" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AC2" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="AD2" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="s">
         <v>123</v>
@@ -3242,42 +3320,458 @@
         <v>42</v>
       </c>
     </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="I3" s="9">
+        <v>1</v>
+      </c>
+      <c r="J3" s="9">
+        <v>1</v>
+      </c>
+      <c r="K3" s="9">
+        <v>0</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="M3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>189</v>
+      </c>
+      <c r="R3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T3" t="s">
+        <v>110</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="W3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X3">
+        <v>9009910202</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>36</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>185</v>
+      </c>
+      <c r="AD3" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="I4" s="9">
+        <v>1</v>
+      </c>
+      <c r="J4" s="9">
+        <v>1</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="M4" t="s">
+        <v>81</v>
+      </c>
+      <c r="N4" t="s">
+        <v>82</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>190</v>
+      </c>
+      <c r="R4" t="s">
+        <v>26</v>
+      </c>
+      <c r="S4" t="s">
+        <v>16</v>
+      </c>
+      <c r="T4" t="s">
+        <v>110</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="W4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4">
+        <v>9009910203</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>186</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>37</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>185</v>
+      </c>
+      <c r="AD4" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" s="9">
+        <v>1</v>
+      </c>
+      <c r="J5" s="9">
+        <v>1</v>
+      </c>
+      <c r="K5" s="9">
+        <v>1</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="M5" t="s">
+        <v>81</v>
+      </c>
+      <c r="N5" t="s">
+        <v>82</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>191</v>
+      </c>
+      <c r="R5" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" t="s">
+        <v>16</v>
+      </c>
+      <c r="T5" t="s">
+        <v>110</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="W5" t="s">
+        <v>24</v>
+      </c>
+      <c r="X5">
+        <v>9009910204</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>38</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="I6" s="9">
+        <v>1</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>1</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="M6" t="s">
+        <v>81</v>
+      </c>
+      <c r="N6" t="s">
+        <v>82</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>192</v>
+      </c>
+      <c r="R6" t="s">
+        <v>26</v>
+      </c>
+      <c r="S6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T6" t="s">
+        <v>110</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="W6" t="s">
+        <v>24</v>
+      </c>
+      <c r="X6">
+        <v>9009910205</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>39</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD6" s="9">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K2" xr:uid="{7E8A2F59-D96B-45A0-82CD-ED332EA05DB5}">
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K6" xr:uid="{7E8A2F59-D96B-45A0-82CD-ED332EA05DB5}">
       <formula1>"0,1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2" xr:uid="{4BEB42D1-92A3-412B-BB52-04798C7EF036}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG6" xr:uid="{4BEB42D1-92A3-412B-BB52-04798C7EF036}">
       <formula1>"Adjustment,Bank Draft,Inter Booking Transfer,Net Banking,Credit Card,Bank Transfer,Debit Card,Cash,Cheque,Direct Deposit"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2" xr:uid="{F75C5611-67EA-46A2-BA00-D17920027D2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC6" xr:uid="{F75C5611-67EA-46A2-BA00-D17920027D2A}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2" xr:uid="{51DBC8A7-7130-4B3D-B204-FA72A8C479D2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD6" xr:uid="{51DBC8A7-7130-4B3D-B204-FA72A8C479D2}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2" xr:uid="{8DA60AD8-7076-451E-89E5-B8FFCAFBB625}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W6" xr:uid="{8DA60AD8-7076-451E-89E5-B8FFCAFBB625}">
       <formula1>"HK,RQ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2" xr:uid="{2F693E2F-7A76-4AB0-9978-694775DE9563}">
-      <formula1>"ABC Supplier,ATsupplier,BSP Supplier,Gaurav Travel"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{C7E15ADA-5B5D-4937-859D-FB8522A37347}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6" xr:uid="{C7E15ADA-5B5D-4937-859D-FB8522A37347}">
       <formula1>"at,qlabs12345,merg123456"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{777455CB-B475-427D-BB45-E83833495EBA}">
-      <formula1>"Piyush_ql,ankur_ql"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{9292DBFF-253C-4A36-A551-4A516AD08ED8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D6" xr:uid="{9292DBFF-253C-4A36-A551-4A516AD08ED8}">
       <formula1>"//xchangev12/backoffice/Home.aspx, //v12staging/backoffice/"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{1E9398B0-F596-4006-917C-F5F41502DFA8}">
-      <formula1>"EE6B4B@E7,Ankur@12345,F1CD@9E4B"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6" xr:uid="{E101ED49-9AA0-44EC-8724-B5E880587B13}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G6" xr:uid="{79474F50-0A72-449E-90DE-3DE344D3060E}">
+      <formula1>"E0@DA44FE,Ankur@721,Piyush@12345"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H6" xr:uid="{975981A6-126B-47A9-9B5F-E450493EBF98}">
+      <formula1>"kumar.gaurav@quadlabs.com,ankit@quadlabs.com,akshay.kumar@quadlabs.com"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R6" xr:uid="{B10DDB98-9E0D-4E9D-8C78-468FE42655E6}">
+      <formula1>"ABC Supplier,ATsupplier,BSP Supplier,gaurav travel"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{3FDBDC7E-63BF-4BA4-BA4A-9D82256C860C}"/>
-    <hyperlink ref="G2" r:id="rId2" xr:uid="{B33B46B8-1A22-4297-B0E7-AEBE7007A78D}"/>
+    <hyperlink ref="H2" r:id="rId1" display="ankit@quadlabs.com" xr:uid="{7FBE733C-D6F2-425A-A8A0-34F3C572786F}"/>
+    <hyperlink ref="G2" r:id="rId2" display="EE6B4B@E7" xr:uid="{6C0616C8-A6B8-474D-87DC-57FE7506C6B9}"/>
+    <hyperlink ref="H3" r:id="rId3" display="ankit@quadlabs.com" xr:uid="{1251DA42-69F2-4607-A98B-96B98194C6F6}"/>
+    <hyperlink ref="G3" r:id="rId4" display="EE6B4B@E7" xr:uid="{5B3FC317-9DD3-4CB3-ADE7-3D2D908167C1}"/>
+    <hyperlink ref="H4" r:id="rId5" display="ankit@quadlabs.com" xr:uid="{98F6BA72-E5B9-437B-BE50-B9F0CAAFFE06}"/>
+    <hyperlink ref="G4" r:id="rId6" display="EE6B4B@E7" xr:uid="{BD20A348-CB77-4A0E-8180-415CC029B000}"/>
+    <hyperlink ref="H5" r:id="rId7" display="ankit@quadlabs.com" xr:uid="{E66CD440-630B-419E-9E3A-A4EDC8535958}"/>
+    <hyperlink ref="G5" r:id="rId8" display="EE6B4B@E7" xr:uid="{8A795A6A-7CA5-4ED6-92C9-E38CDFEBFCA6}"/>
+    <hyperlink ref="H6" r:id="rId9" display="ankit@quadlabs.com" xr:uid="{7A66936C-608B-4E65-BBEA-E8321AD59A9C}"/>
+    <hyperlink ref="G6" r:id="rId10" display="EE6B4B@E7" xr:uid="{574A3DF3-6C09-497B-ABD5-E5EF9E224DB9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3403,32 +3897,32 @@
       <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>144</v>
+      <c r="F2" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>141</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I2" s="20">
-        <v>1</v>
-      </c>
-      <c r="J2" s="20">
+        <v>136</v>
+      </c>
+      <c r="I2" s="15">
+        <v>1</v>
+      </c>
+      <c r="J2" s="15">
         <v>0</v>
       </c>
-      <c r="K2" s="20">
+      <c r="K2" s="15">
         <v>0</v>
       </c>
-      <c r="L2" s="20" t="s">
-        <v>153</v>
+      <c r="L2" s="15" t="s">
+        <v>150</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>81</v>
@@ -3436,10 +3930,10 @@
       <c r="N2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="16" t="s">
         <v>84</v>
       </c>
       <c r="Q2" s="3" t="s">
@@ -3454,11 +3948,11 @@
       <c r="T2" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="U2" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="V2" s="21" t="s">
-        <v>141</v>
+      <c r="U2" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="V2" s="16" t="s">
+        <v>138</v>
       </c>
       <c r="W2" s="3" t="s">
         <v>24</v>
@@ -3467,10 +3961,10 @@
         <v>9999999112</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AA2" s="3">
         <v>1</v>
@@ -3481,14 +3975,14 @@
       <c r="AC2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AD2" s="20">
+      <c r="AD2" s="15">
         <v>1</v>
       </c>
       <c r="AE2" s="3" t="s">
         <v>123</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="AG2" s="3" t="s">
         <v>42</v>
@@ -3504,47 +3998,47 @@
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>144</v>
+      <c r="F3" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>141</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I3" s="20">
-        <v>1</v>
-      </c>
-      <c r="J3" s="20">
-        <v>1</v>
-      </c>
-      <c r="K3" s="20">
+        <v>136</v>
+      </c>
+      <c r="I3" s="15">
+        <v>1</v>
+      </c>
+      <c r="J3" s="15">
+        <v>1</v>
+      </c>
+      <c r="K3" s="15">
         <v>0</v>
       </c>
-      <c r="L3" s="20" t="s">
-        <v>149</v>
+      <c r="L3" s="15" t="s">
+        <v>146</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O3" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="P3" s="21" t="s">
-        <v>158</v>
+      <c r="P3" s="16" t="s">
+        <v>155</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>26</v>
@@ -3555,11 +4049,11 @@
       <c r="T3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="U3" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="V3" s="21" t="s">
-        <v>171</v>
+      <c r="U3" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="V3" s="16" t="s">
+        <v>168</v>
       </c>
       <c r="W3" s="3" t="s">
         <v>24</v>
@@ -3568,10 +4062,10 @@
         <v>9999999113</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AA3" s="3">
         <v>1</v>
@@ -3582,14 +4076,14 @@
       <c r="AC3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AD3" s="20">
+      <c r="AD3" s="15">
         <v>2</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AG3" s="3" t="s">
         <v>42</v>
@@ -3605,50 +4099,50 @@
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>144</v>
+      <c r="F4" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>141</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I4" s="20">
-        <v>1</v>
-      </c>
-      <c r="J4" s="20">
-        <v>1</v>
-      </c>
-      <c r="K4" s="20">
-        <v>1</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>156</v>
+        <v>136</v>
+      </c>
+      <c r="I4" s="15">
+        <v>1</v>
+      </c>
+      <c r="J4" s="15">
+        <v>1</v>
+      </c>
+      <c r="K4" s="15">
+        <v>1</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>153</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q4" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="O4" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="P4" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="R4" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>16</v>
@@ -3656,11 +4150,11 @@
       <c r="T4" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="U4" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="V4" s="21" t="s">
-        <v>162</v>
+      <c r="U4" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="V4" s="16" t="s">
+        <v>159</v>
       </c>
       <c r="W4" s="3" t="s">
         <v>24</v>
@@ -3669,10 +4163,10 @@
         <v>9999999114</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AA4" s="3">
         <v>1</v>
@@ -3683,14 +4177,14 @@
       <c r="AC4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AD4" s="20">
+      <c r="AD4" s="15">
         <v>3</v>
       </c>
       <c r="AE4" s="3" t="s">
         <v>123</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AG4" s="3" t="s">
         <v>42</v>
@@ -3895,20 +4389,20 @@
       <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>138</v>
+      <c r="F2" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>135</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -3996,20 +4490,20 @@
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>138</v>
+      <c r="F3" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>135</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I3" s="9">
         <v>1</v>
@@ -4097,20 +4591,20 @@
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>138</v>
+      <c r="F4" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>135</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I4" s="9">
         <v>1</v>
@@ -4198,20 +4692,20 @@
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>138</v>
+      <c r="F5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>135</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I5" s="9">
         <v>2</v>
@@ -4299,20 +4793,20 @@
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>138</v>
+      <c r="F6" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>135</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I6" s="9">
         <v>2</v>
@@ -4553,20 +5047,20 @@
       <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>144</v>
+      <c r="F2" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>141</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I2" s="9">
         <v>1</v>
@@ -4578,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M2" t="s">
         <v>81</v>
@@ -4596,7 +5090,7 @@
         <v>107</v>
       </c>
       <c r="R2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="S2" t="s">
         <v>16</v>
@@ -4605,10 +5099,10 @@
         <v>110</v>
       </c>
       <c r="U2" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="V2" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="W2" t="s">
         <v>24</v>
@@ -4617,10 +5111,10 @@
         <v>9999999104</v>
       </c>
       <c r="Y2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="Z2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AA2">
         <v>1</v>
